--- a/salidas/empresas/BKNG.xlsx
+++ b/salidas/empresas/BKNG.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8615735769271851</v>
+        <v>0.8615734577178955</v>
       </c>
       <c r="C2" t="n">
         <v>0.8820000290870667</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>0.9592575430870056</v>
+        <v>0.9592574834823608</v>
       </c>
       <c r="C3" t="n">
         <v>0.9819999933242798</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>0.9705889225006104</v>
+        <v>0.970588743686676</v>
       </c>
       <c r="C4" t="n">
         <v>0.9936000108718872</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>0.9549594521522522</v>
+        <v>0.9549593925476074</v>
       </c>
       <c r="C5" t="n">
         <v>0.9775999784469604</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>1.215189814567566</v>
+        <v>1.215189695358276</v>
       </c>
       <c r="C6" t="n">
         <v>1.24399995803833</v>
@@ -577,7 +589,7 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
@@ -596,7 +608,7 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
@@ -615,7 +627,7 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>1.43751847743988</v>
+        <v>1.437518835067749</v>
       </c>
       <c r="C10" t="n">
         <v>1.47160005569458</v>
@@ -653,7 +665,7 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>1.543017268180847</v>
+        <v>1.543017387390137</v>
       </c>
       <c r="C12" t="n">
         <v>1.579599976539612</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>1.704000949859619</v>
+        <v>1.70400071144104</v>
       </c>
       <c r="C13" t="n">
         <v>1.744400024414062</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>1.665318012237549</v>
+        <v>1.665317893028259</v>
       </c>
       <c r="C14" t="n">
         <v>1.704800009727478</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>2.047848701477051</v>
+        <v>2.04784893989563</v>
       </c>
       <c r="C15" t="n">
         <v>2.096400022506714</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>2.081061601638794</v>
+        <v>2.081061124801636</v>
       </c>
       <c r="C16" t="n">
         <v>2.130399942398071</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>2.174056529998779</v>
+        <v>2.174056053161621</v>
       </c>
       <c r="C17" t="n">
         <v>2.225600004196167</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>2.41631293296814</v>
+        <v>2.416312456130981</v>
       </c>
       <c r="C18" t="n">
         <v>2.473599910736084</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>2.685920715332031</v>
+        <v>2.685920476913452</v>
       </c>
       <c r="C19" t="n">
         <v>2.749599933624268</v>
@@ -824,7 +836,7 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
@@ -843,7 +855,7 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>3.467784881591797</v>
+        <v>3.46778416633606</v>
       </c>
       <c r="C22" t="n">
         <v>3.549999952316284</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>3.637754440307617</v>
+        <v>3.637754678726196</v>
       </c>
       <c r="C23" t="n">
         <v>3.723999977111816</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>4.446578979492188</v>
+        <v>4.446578502655029</v>
       </c>
       <c r="C24" t="n">
         <v>4.552000045776367</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>4.487996101379395</v>
+        <v>4.487997055053711</v>
       </c>
       <c r="C25" t="n">
         <v>4.594399929046631</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>4.240270614624023</v>
+        <v>4.240269660949707</v>
       </c>
       <c r="C26" t="n">
         <v>4.340799808502197</v>
@@ -957,7 +969,7 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>4.722438335418701</v>
+        <v>4.722438812255859</v>
       </c>
       <c r="C28" t="n">
         <v>4.834400177001953</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>4.987357616424561</v>
+        <v>4.987357139587402</v>
       </c>
       <c r="C29" t="n">
         <v>5.105599880218506</v>
@@ -1014,7 +1026,7 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>4.511440753936768</v>
+        <v>4.511441230773926</v>
       </c>
       <c r="C31" t="n">
         <v>4.618400096893311</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>4.491513252258301</v>
+        <v>4.491513729095459</v>
       </c>
       <c r="C32" t="n">
         <v>4.598000049591064</v>
@@ -1071,7 +1083,7 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>2.673807859420776</v>
+        <v>2.673808097839355</v>
       </c>
       <c r="C34" t="n">
         <v>2.737200021743774</v>
@@ -1109,7 +1121,7 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
@@ -1128,7 +1140,7 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>2.87777304649353</v>
+        <v>2.877772808074951</v>
       </c>
       <c r="C37" t="n">
         <v>2.946000099182129</v>
@@ -1166,7 +1178,7 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>3.315787553787231</v>
+        <v>3.31578803062439</v>
       </c>
       <c r="C39" t="n">
         <v>3.394399881362915</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>3.078220367431641</v>
+        <v>3.078220129013062</v>
       </c>
       <c r="C40" t="n">
         <v>3.15120005607605</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>3.793658018112183</v>
+        <v>3.793657779693604</v>
       </c>
       <c r="C41" t="n">
         <v>3.883599996566772</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>4.30239725112915</v>
+        <v>4.302396774291992</v>
       </c>
       <c r="C42" t="n">
         <v>4.404399871826172</v>
@@ -1261,7 +1273,7 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>5.064723014831543</v>
+        <v>5.064723491668701</v>
       </c>
       <c r="C44" t="n">
         <v>5.184800148010254</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>6.016557216644287</v>
+        <v>6.016557693481445</v>
       </c>
       <c r="C45" t="n">
         <v>6.159200191497803</v>
@@ -1318,11 +1330,11 @@
       <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>6.479188442230225</v>
+        <v>6.479188919067383</v>
       </c>
       <c r="C46" t="n">
         <v>6.632800102233887</v>
@@ -1337,7 +1349,7 @@
       <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
@@ -1356,11 +1368,11 @@
       <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>8.366445541381836</v>
+        <v>8.36644458770752</v>
       </c>
       <c r="C48" t="n">
         <v>8.564800262451172</v>
@@ -1375,11 +1387,11 @@
       <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>8.53407096862793</v>
+        <v>8.534069061279297</v>
       </c>
       <c r="C49" t="n">
         <v>8.73639965057373</v>
@@ -1394,11 +1406,11 @@
       <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>7.633032321929932</v>
+        <v>7.633033275604248</v>
       </c>
       <c r="C50" t="n">
         <v>7.814000129699707</v>
@@ -1413,11 +1425,11 @@
       <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>8.858381271362305</v>
+        <v>8.858382225036621</v>
       </c>
       <c r="C51" t="n">
         <v>9.068400382995605</v>
@@ -1432,11 +1444,11 @@
       <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>9.963772773742676</v>
+        <v>9.963773727416992</v>
       </c>
       <c r="C52" t="n">
         <v>10.19999980926514</v>
@@ -1451,11 +1463,11 @@
       <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>10.23924446105957</v>
+        <v>10.23924255371094</v>
       </c>
       <c r="C53" t="n">
         <v>10.48200035095215</v>
@@ -1470,7 +1482,7 @@
       <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
@@ -1489,11 +1501,11 @@
       <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>6.898058414459229</v>
+        <v>6.898058891296387</v>
       </c>
       <c r="C55" t="n">
         <v>7.061600208282471</v>
@@ -1508,11 +1520,11 @@
       <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>8.768121719360352</v>
+        <v>8.768122673034668</v>
       </c>
       <c r="C56" t="n">
         <v>8.97599983215332</v>
@@ -1527,11 +1539,11 @@
       <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>11.38918113708496</v>
+        <v>11.38917922973633</v>
       </c>
       <c r="C57" t="n">
         <v>11.65919971466064</v>
@@ -1552,11 +1564,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>13.61090755462646</v>
+        <v>13.61090564727783</v>
       </c>
       <c r="C58" t="n">
         <v>13.93360042572021</v>
@@ -1577,7 +1589,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
@@ -1602,7 +1614,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
@@ -1627,11 +1639,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>15.61186790466309</v>
+        <v>15.61186695098877</v>
       </c>
       <c r="C61" t="n">
         <v>15.98200035095215</v>
@@ -1652,11 +1664,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>16.74383163452148</v>
+        <v>16.74382972717285</v>
       </c>
       <c r="C62" t="n">
         <v>17.14080047607422</v>
@@ -1677,11 +1689,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>17.73473739624023</v>
+        <v>17.7347354888916</v>
       </c>
       <c r="C63" t="n">
         <v>18.15519905090332</v>
@@ -1706,11 +1718,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>19.78845024108887</v>
+        <v>19.7884464263916</v>
       </c>
       <c r="C64" t="n">
         <v>20.25760078430176</v>
@@ -1735,7 +1747,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
@@ -1764,11 +1776,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>20.13034057617188</v>
+        <v>20.13034248352051</v>
       </c>
       <c r="C66" t="n">
         <v>20.60759925842285</v>
@@ -1793,7 +1805,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
@@ -1822,11 +1834,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>21.00793647766113</v>
+        <v>21.00793266296387</v>
       </c>
       <c r="C68" t="n">
         <v>21.50600051879883</v>
@@ -1851,11 +1863,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>20.99269485473633</v>
+        <v>20.99269676208496</v>
       </c>
       <c r="C69" t="n">
         <v>21.49040031433105</v>
@@ -1880,7 +1892,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
@@ -1909,7 +1921,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
@@ -1938,11 +1950,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>18.98548698425293</v>
+        <v>18.9854850769043</v>
       </c>
       <c r="C72" t="n">
         <v>19.43560028076172</v>
@@ -1967,11 +1979,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>18.27512359619141</v>
+        <v>18.27512550354004</v>
       </c>
       <c r="C73" t="n">
         <v>18.70840072631836</v>
@@ -1996,11 +2008,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>20.6890926361084</v>
+        <v>20.68909454345703</v>
       </c>
       <c r="C74" t="n">
         <v>21.17959976196289</v>
@@ -2025,11 +2037,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>24.49993896484375</v>
+        <v>24.49994087219238</v>
       </c>
       <c r="C75" t="n">
         <v>25.0807991027832</v>
@@ -2054,11 +2066,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>28.03532600402832</v>
+        <v>28.03532791137695</v>
       </c>
       <c r="C76" t="n">
         <v>28.70000076293945</v>
@@ -2083,11 +2095,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>29.72799873352051</v>
+        <v>29.72799491882324</v>
       </c>
       <c r="C77" t="n">
         <v>30.43280029296875</v>
@@ -2112,11 +2124,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>24.44015884399414</v>
+        <v>24.44016075134277</v>
       </c>
       <c r="C78" t="n">
         <v>25.01959991455078</v>
@@ -2141,11 +2153,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>25.96520233154297</v>
+        <v>25.96520614624023</v>
       </c>
       <c r="C79" t="n">
         <v>26.5807991027832</v>
@@ -2170,7 +2182,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
@@ -2199,11 +2211,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>23.62274360656738</v>
+        <v>23.62273979187012</v>
       </c>
       <c r="C81" t="n">
         <v>24.18280029296875</v>
@@ -2228,11 +2240,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>24.18931007385254</v>
+        <v>24.18931198120117</v>
       </c>
       <c r="C82" t="n">
         <v>24.7628002166748</v>
@@ -2257,11 +2269,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>22.41927146911621</v>
+        <v>22.41927528381348</v>
       </c>
       <c r="C83" t="n">
         <v>22.9507999420166</v>
@@ -2286,11 +2298,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>25.91323852539062</v>
+        <v>25.91323661804199</v>
       </c>
       <c r="C84" t="n">
         <v>26.5275993347168</v>
@@ -2315,11 +2327,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>24.24088478088379</v>
+        <v>24.24088668823242</v>
       </c>
       <c r="C85" t="n">
         <v>24.81559944152832</v>
@@ -2344,11 +2356,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>26.7837963104248</v>
+        <v>26.78380012512207</v>
       </c>
       <c r="C86" t="n">
         <v>27.41880035400391</v>
@@ -2373,11 +2385,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>26.92602729797363</v>
+        <v>26.926025390625</v>
       </c>
       <c r="C87" t="n">
         <v>27.56439971923828</v>
@@ -2402,11 +2414,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>26.88890647888184</v>
+        <v>26.88890838623047</v>
       </c>
       <c r="C88" t="n">
         <v>27.52639961242676</v>
@@ -2431,11 +2443,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>27.19485473632812</v>
+        <v>27.19484901428223</v>
       </c>
       <c r="C89" t="n">
         <v>27.839599609375</v>
@@ -2460,7 +2472,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
@@ -2489,7 +2501,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
@@ -2518,11 +2530,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>34.21559906005859</v>
+        <v>34.21560287475586</v>
       </c>
       <c r="C92" t="n">
         <v>35.02679824829102</v>
@@ -2547,11 +2559,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>36.67176818847656</v>
+        <v>36.67177200317383</v>
       </c>
       <c r="C93" t="n">
         <v>37.54119873046875</v>
@@ -2576,11 +2588,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>39.50148773193359</v>
+        <v>39.50148391723633</v>
       </c>
       <c r="C94" t="n">
         <v>40.4379997253418</v>
@@ -2605,11 +2617,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>41.17695617675781</v>
+        <v>41.17695236206055</v>
       </c>
       <c r="C95" t="n">
         <v>42.1531982421875</v>
@@ -2634,7 +2646,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
@@ -2663,7 +2675,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
@@ -2692,11 +2704,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>44.73500823974609</v>
+        <v>44.73500442504883</v>
       </c>
       <c r="C98" t="n">
         <v>45.79560089111328</v>
@@ -2721,7 +2733,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
@@ -2750,11 +2762,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>46.57146072387695</v>
+        <v>46.57145690917969</v>
       </c>
       <c r="C100" t="n">
         <v>47.67559814453125</v>
@@ -2779,11 +2791,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>45.23749160766602</v>
+        <v>45.23748779296875</v>
       </c>
       <c r="C101" t="n">
         <v>46.31000137329102</v>
@@ -2808,7 +2820,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
@@ -2837,11 +2849,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>47.00556945800781</v>
+        <v>47.00556564331055</v>
       </c>
       <c r="C103" t="n">
         <v>48.11999893188477</v>
@@ -2866,11 +2878,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>48.54702377319336</v>
+        <v>48.54701995849609</v>
       </c>
       <c r="C104" t="n">
         <v>49.69800186157227</v>
@@ -2895,7 +2907,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
@@ -2924,11 +2936,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>45.26992416381836</v>
+        <v>45.26991271972656</v>
       </c>
       <c r="C106" t="n">
         <v>46.34320068359375</v>
@@ -2953,11 +2965,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>47.13100051879883</v>
+        <v>47.1309928894043</v>
       </c>
       <c r="C107" t="n">
         <v>48.2484016418457</v>
@@ -2982,7 +2994,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
@@ -3011,11 +3023,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>44.55214309692383</v>
+        <v>44.5521354675293</v>
       </c>
       <c r="C109" t="n">
         <v>45.6083984375</v>
@@ -3040,11 +3052,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>39.44403839111328</v>
+        <v>39.44404602050781</v>
       </c>
       <c r="C110" t="n">
         <v>40.37919998168945</v>
@@ -3069,11 +3081,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>48.35282897949219</v>
+        <v>48.35282516479492</v>
       </c>
       <c r="C111" t="n">
         <v>49.49919891357422</v>
@@ -3098,11 +3110,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>45.48755645751953</v>
+        <v>45.4875602722168</v>
       </c>
       <c r="C112" t="n">
         <v>46.56600189208984</v>
@@ -3127,7 +3139,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
@@ -3156,11 +3168,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>45.79585647583008</v>
+        <v>45.79585266113281</v>
       </c>
       <c r="C114" t="n">
         <v>46.88159942626953</v>
@@ -3185,11 +3197,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>44.98819351196289</v>
+        <v>44.98819732666016</v>
       </c>
       <c r="C115" t="n">
         <v>46.0547981262207</v>
@@ -3214,11 +3226,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>48.59078598022461</v>
+        <v>48.59078216552734</v>
       </c>
       <c r="C116" t="n">
         <v>49.74280166625977</v>
@@ -3243,7 +3255,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
@@ -3272,11 +3284,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>48.32860946655273</v>
+        <v>48.32859802246094</v>
       </c>
       <c r="C118" t="n">
         <v>49.47439956665039</v>
@@ -3301,11 +3313,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>56.82243347167969</v>
+        <v>56.82242965698242</v>
       </c>
       <c r="C119" t="n">
         <v>58.16960144042969</v>
@@ -3330,7 +3342,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
@@ -3359,11 +3371,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>49.81692123413086</v>
+        <v>49.81691741943359</v>
       </c>
       <c r="C121" t="n">
         <v>50.99800109863281</v>
@@ -3388,7 +3400,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
@@ -3417,7 +3429,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
@@ -3446,7 +3458,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
@@ -3475,11 +3487,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>52.50166702270508</v>
+        <v>52.50167083740234</v>
       </c>
       <c r="C125" t="n">
         <v>53.74639892578125</v>
@@ -3504,11 +3516,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>49.40196228027344</v>
+        <v>49.40195083618164</v>
       </c>
       <c r="C126" t="n">
         <v>50.57320022583008</v>
@@ -3533,11 +3545,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>48.77990341186523</v>
+        <v>48.77989959716797</v>
       </c>
       <c r="C127" t="n">
         <v>49.9364013671875</v>
@@ -3562,11 +3574,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>52.78104019165039</v>
+        <v>52.78104400634766</v>
       </c>
       <c r="C128" t="n">
         <v>54.03239822387695</v>
@@ -3591,11 +3603,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>55.35677719116211</v>
+        <v>55.35678482055664</v>
       </c>
       <c r="C129" t="n">
         <v>56.6692008972168</v>
@@ -3620,7 +3632,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
@@ -3649,11 +3661,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>57.60351181030273</v>
+        <v>57.6035041809082</v>
       </c>
       <c r="C131" t="n">
         <v>58.96920013427734</v>
@@ -3678,11 +3690,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>58.75423812866211</v>
+        <v>58.75423431396484</v>
       </c>
       <c r="C132" t="n">
         <v>60.14720153808594</v>
@@ -3707,11 +3719,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>57.28427886962891</v>
+        <v>57.28427505493164</v>
       </c>
       <c r="C133" t="n">
         <v>58.64239883422852</v>
@@ -3736,11 +3748,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>61.5460319519043</v>
+        <v>61.54603576660156</v>
       </c>
       <c r="C134" t="n">
         <v>63.00519943237305</v>
@@ -3765,7 +3777,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
@@ -3794,11 +3806,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>69.54988861083984</v>
+        <v>69.54988098144531</v>
       </c>
       <c r="C136" t="n">
         <v>71.19879913330078</v>
@@ -3823,11 +3835,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>72.16194152832031</v>
+        <v>72.16194915771484</v>
       </c>
       <c r="C137" t="n">
         <v>73.872802734375</v>
@@ -3852,7 +3864,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
@@ -3881,11 +3893,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>73.08798217773438</v>
+        <v>73.08800506591797</v>
       </c>
       <c r="C139" t="n">
         <v>74.82080078125</v>
@@ -3910,11 +3922,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>79.26084136962891</v>
+        <v>79.26084899902344</v>
       </c>
       <c r="C140" t="n">
         <v>81.13999938964844</v>
@@ -3939,11 +3951,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>72.36747741699219</v>
+        <v>72.36748504638672</v>
       </c>
       <c r="C141" t="n">
         <v>74.08319854736328</v>
@@ -3968,7 +3980,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
@@ -3997,7 +4009,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
@@ -4026,11 +4038,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>67.97676849365234</v>
+        <v>67.97677612304688</v>
       </c>
       <c r="C144" t="n">
         <v>69.58840179443359</v>
@@ -4055,11 +4067,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>67.89981079101562</v>
+        <v>67.89979553222656</v>
       </c>
       <c r="C145" t="n">
         <v>69.50959777832031</v>
@@ -4084,11 +4096,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>74.71072387695312</v>
+        <v>74.71073913574219</v>
       </c>
       <c r="C146" t="n">
         <v>76.48200225830078</v>
@@ -4113,11 +4125,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>79.47732543945312</v>
+        <v>79.47731018066406</v>
       </c>
       <c r="C147" t="n">
         <v>81.36160278320312</v>
@@ -4142,11 +4154,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>81.28838348388672</v>
+        <v>81.28837585449219</v>
       </c>
       <c r="C148" t="n">
         <v>83.21559906005859</v>
@@ -4171,11 +4183,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>85.10237121582031</v>
+        <v>85.10235595703125</v>
       </c>
       <c r="C149" t="n">
         <v>87.12000274658203</v>
@@ -4200,11 +4212,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>82.40314483642578</v>
+        <v>82.40316009521484</v>
       </c>
       <c r="C150" t="n">
         <v>84.35679626464844</v>
@@ -4229,7 +4241,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
@@ -4258,11 +4270,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>79.26944732666016</v>
+        <v>79.26946258544922</v>
       </c>
       <c r="C152" t="n">
         <v>81.1488037109375</v>
@@ -4287,11 +4299,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>76.25412750244141</v>
+        <v>76.25413513183594</v>
       </c>
       <c r="C153" t="n">
         <v>78.06199645996094</v>
@@ -4316,7 +4328,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
@@ -4345,11 +4357,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>73.24664306640625</v>
+        <v>73.24663543701172</v>
       </c>
       <c r="C155" t="n">
         <v>74.98320007324219</v>
@@ -4374,11 +4386,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>73.922607421875</v>
+        <v>73.92262268066406</v>
       </c>
       <c r="C156" t="n">
         <v>75.67520141601562</v>
@@ -4403,11 +4415,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>67.30117797851562</v>
+        <v>67.30118560791016</v>
       </c>
       <c r="C157" t="n">
         <v>68.89679718017578</v>
@@ -4432,11 +4444,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>71.61454772949219</v>
+        <v>71.61453247070312</v>
       </c>
       <c r="C158" t="n">
         <v>73.31240081787109</v>
@@ -4461,11 +4473,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>66.30950927734375</v>
+        <v>66.30949401855469</v>
       </c>
       <c r="C159" t="n">
         <v>67.88159942626953</v>
@@ -4490,11 +4502,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>68.17995452880859</v>
+        <v>68.17996978759766</v>
       </c>
       <c r="C160" t="n">
         <v>69.79640197753906</v>
@@ -4519,11 +4531,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>72.48117828369141</v>
+        <v>72.48118591308594</v>
       </c>
       <c r="C161" t="n">
         <v>74.19960021972656</v>
@@ -4548,11 +4560,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>64.71451568603516</v>
+        <v>64.71453094482422</v>
       </c>
       <c r="C162" t="n">
         <v>66.24880218505859</v>
@@ -4577,11 +4589,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>73.25172424316406</v>
+        <v>73.251708984375</v>
       </c>
       <c r="C163" t="n">
         <v>74.9884033203125</v>
@@ -4606,7 +4618,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
@@ -4635,7 +4647,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
@@ -4664,11 +4676,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>76.68629455566406</v>
+        <v>76.68628692626953</v>
       </c>
       <c r="C166" t="n">
         <v>78.50440216064453</v>
@@ -4693,11 +4705,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>80.05286407470703</v>
+        <v>80.05287170410156</v>
       </c>
       <c r="C167" t="n">
         <v>81.95079803466797</v>
@@ -4722,7 +4734,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
@@ -4751,11 +4763,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>80.24666595458984</v>
+        <v>80.24667358398438</v>
       </c>
       <c r="C169" t="n">
         <v>82.14920043945312</v>
@@ -4780,11 +4792,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>71.52621459960938</v>
+        <v>71.52623748779297</v>
       </c>
       <c r="C170" t="n">
         <v>73.22200012207031</v>
@@ -4809,11 +4821,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>66.25556945800781</v>
+        <v>66.25558471679688</v>
       </c>
       <c r="C171" t="n">
         <v>67.82640075683594</v>
@@ -4838,7 +4850,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
@@ -4867,11 +4879,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>57.85123825073242</v>
+        <v>57.85124206542969</v>
       </c>
       <c r="C173" t="n">
         <v>59.22280120849609</v>
@@ -4896,11 +4908,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>64.05806732177734</v>
+        <v>64.05808258056641</v>
       </c>
       <c r="C174" t="n">
         <v>65.57679748535156</v>
@@ -4925,11 +4937,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>62.2184944152832</v>
+        <v>62.21849060058594</v>
       </c>
       <c r="C175" t="n">
         <v>63.69359970092773</v>
@@ -4954,11 +4966,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>64.9454345703125</v>
+        <v>64.94544219970703</v>
       </c>
       <c r="C176" t="n">
         <v>66.48519897460938</v>
@@ -4983,11 +4995,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>74.64820861816406</v>
+        <v>74.64821624755859</v>
       </c>
       <c r="C177" t="n">
         <v>76.41799926757812</v>
@@ -5012,11 +5024,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>66.84246826171875</v>
+        <v>66.84247589111328</v>
       </c>
       <c r="C178" t="n">
         <v>68.42720031738281</v>
@@ -5041,11 +5053,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>63.39695358276367</v>
+        <v>63.39694976806641</v>
       </c>
       <c r="C179" t="n">
         <v>64.90000152587891</v>
@@ -5070,11 +5082,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>79.25889587402344</v>
+        <v>79.25888824462891</v>
       </c>
       <c r="C180" t="n">
         <v>81.13800048828125</v>
@@ -5099,11 +5111,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>87.02751922607422</v>
+        <v>87.02751159667969</v>
       </c>
       <c r="C181" t="n">
         <v>89.09079742431641</v>
@@ -5128,11 +5140,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>75.97202301025391</v>
+        <v>75.97203063964844</v>
       </c>
       <c r="C182" t="n">
         <v>77.77320098876953</v>
@@ -5157,7 +5169,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
@@ -5186,11 +5198,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>91.03530120849609</v>
+        <v>91.03529357910156</v>
       </c>
       <c r="C184" t="n">
         <v>93.193603515625</v>
@@ -5215,11 +5227,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>96.35868835449219</v>
+        <v>96.35869598388672</v>
       </c>
       <c r="C185" t="n">
         <v>98.64320373535156</v>
@@ -5244,11 +5256,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>92.27431488037109</v>
+        <v>92.27430725097656</v>
       </c>
       <c r="C186" t="n">
         <v>94.46199798583984</v>
@@ -5273,7 +5285,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
@@ -5302,7 +5314,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
@@ -5331,7 +5343,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
@@ -5360,7 +5372,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
@@ -5389,11 +5401,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>94.58865356445312</v>
+        <v>94.58864593505859</v>
       </c>
       <c r="C191" t="n">
         <v>96.83119964599609</v>
@@ -5418,11 +5430,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>82.12690734863281</v>
+        <v>82.12689971923828</v>
       </c>
       <c r="C192" t="n">
         <v>84.07399749755859</v>
@@ -5447,7 +5459,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
@@ -5476,11 +5488,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>95.96990966796875</v>
+        <v>95.96990203857422</v>
       </c>
       <c r="C194" t="n">
         <v>98.24520111083984</v>
@@ -5505,11 +5517,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>84.87767791748047</v>
+        <v>84.87769317626953</v>
       </c>
       <c r="C195" t="n">
         <v>86.88999938964844</v>
@@ -5534,11 +5546,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>91.76245880126953</v>
+        <v>91.762451171875</v>
       </c>
       <c r="C196" t="n">
         <v>93.93800354003906</v>
@@ -5563,7 +5575,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
@@ -5592,11 +5604,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>87.66403198242188</v>
+        <v>87.66402435302734</v>
       </c>
       <c r="C198" t="n">
         <v>89.74240112304688</v>
@@ -5621,7 +5633,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
@@ -5650,11 +5662,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>75.63441467285156</v>
+        <v>75.63442230224609</v>
       </c>
       <c r="C200" t="n">
         <v>77.42759704589844</v>
@@ -5679,11 +5691,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>73.29469299316406</v>
+        <v>73.29468536376953</v>
       </c>
       <c r="C201" t="n">
         <v>75.03240203857422</v>
@@ -5708,11 +5720,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>64.20616912841797</v>
+        <v>64.20616149902344</v>
       </c>
       <c r="C202" t="n">
         <v>65.72840118408203</v>
@@ -5737,11 +5749,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>73.04734039306641</v>
+        <v>73.04735565185547</v>
       </c>
       <c r="C203" t="n">
         <v>74.77919769287109</v>
@@ -5766,11 +5778,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>81.25164794921875</v>
+        <v>81.25165557861328</v>
       </c>
       <c r="C204" t="n">
         <v>83.17800140380859</v>
@@ -5795,11 +5807,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>78.74428558349609</v>
+        <v>78.74429321289062</v>
       </c>
       <c r="C205" t="n">
         <v>80.61119842529297</v>
@@ -5824,7 +5836,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
@@ -5853,11 +5865,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>98.62184143066406</v>
+        <v>98.62181854248047</v>
       </c>
       <c r="C207" t="n">
         <v>100.9599990844727</v>
@@ -5882,11 +5894,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>103.639274597168</v>
+        <v>103.6392669677734</v>
       </c>
       <c r="C208" t="n">
         <v>106.0963973999023</v>
@@ -5911,7 +5923,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
@@ -5940,7 +5952,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
@@ -5969,11 +5981,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>105.5116729736328</v>
+        <v>105.5116806030273</v>
       </c>
       <c r="C211" t="n">
         <v>108.0131988525391</v>
@@ -5998,11 +6010,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>116.0799255371094</v>
+        <v>116.0799331665039</v>
       </c>
       <c r="C212" t="n">
         <v>118.8320007324219</v>
@@ -6027,7 +6039,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
@@ -6056,11 +6068,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>120.5010986328125</v>
+        <v>120.501106262207</v>
       </c>
       <c r="C214" t="n">
         <v>123.3580017089844</v>
@@ -6085,11 +6097,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>108.9982147216797</v>
+        <v>108.9982223510742</v>
       </c>
       <c r="C215" t="n">
         <v>111.5823974609375</v>
@@ -6114,11 +6126,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>122.1324234008789</v>
+        <v>122.132438659668</v>
       </c>
       <c r="C216" t="n">
         <v>125.0279998779297</v>
@@ -6143,11 +6155,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>138.6027221679688</v>
+        <v>138.6027526855469</v>
       </c>
       <c r="C217" t="n">
         <v>141.8887939453125</v>
@@ -6172,7 +6184,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
@@ -6201,11 +6213,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>135.5397796630859</v>
+        <v>135.5397644042969</v>
       </c>
       <c r="C219" t="n">
         <v>138.7532043457031</v>
@@ -6230,7 +6242,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
@@ -6259,11 +6271,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>135.228515625</v>
+        <v>135.2284851074219</v>
       </c>
       <c r="C221" t="n">
         <v>138.0812072753906</v>
@@ -6288,11 +6300,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>147.9332885742188</v>
+        <v>147.9333038330078</v>
       </c>
       <c r="C222" t="n">
         <v>151.0540008544922</v>
@@ -6317,7 +6329,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
@@ -6346,7 +6358,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
@@ -6375,11 +6387,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>153.4911956787109</v>
+        <v>153.4911804199219</v>
       </c>
       <c r="C225" t="n">
         <v>156.3692016601562</v>
@@ -6404,7 +6416,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
@@ -6433,11 +6445,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>184.0330657958984</v>
+        <v>184.0330963134766</v>
       </c>
       <c r="C227" t="n">
         <v>187.0500030517578</v>
@@ -6462,7 +6474,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
@@ -6491,11 +6503,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>195.8554382324219</v>
+        <v>195.8554534912109</v>
       </c>
       <c r="C229" t="n">
         <v>198.7368011474609</v>
@@ -6520,7 +6532,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
@@ -6549,7 +6561,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6578,11 +6590,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>181.9767456054688</v>
+        <v>181.9767303466797</v>
       </c>
       <c r="C232" t="n">
         <v>184.2763977050781</v>
@@ -6607,11 +6619,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>201.42578125</v>
+        <v>201.4257507324219</v>
       </c>
       <c r="C233" t="n">
         <v>203.9712066650391</v>
@@ -6636,11 +6648,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>218.0022430419922</v>
+        <v>218.0022888183594</v>
       </c>
       <c r="C234" t="n">
         <v>220.7572021484375</v>
@@ -6665,11 +6677,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>229.0745239257812</v>
+        <v>229.0744934082031</v>
       </c>
       <c r="C235" t="n">
         <v>231.5695953369141</v>
@@ -6694,11 +6706,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>217.7902069091797</v>
+        <v>217.7902221679688</v>
       </c>
       <c r="C236" t="n">
         <v>220.1623992919922</v>
@@ -6723,11 +6735,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>221.5489044189453</v>
+        <v>221.5488891601562</v>
       </c>
       <c r="C237" t="n">
         <v>223.9620056152344</v>
@@ -6752,7 +6764,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6781,7 +6793,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6810,11 +6822,11 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>194.8042449951172</v>
+        <v>194.8042297363281</v>
       </c>
       <c r="C240" t="n">
         <v>196.5876007080078</v>
@@ -6839,7 +6851,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6868,7 +6880,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6897,7 +6909,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6926,7 +6938,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -6955,7 +6967,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -6984,7 +6996,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7013,7 +7025,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7042,7 +7054,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7071,7 +7083,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7100,32 +7112,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>155.8999938964844</v>
+        <v>157.4100036621094</v>
       </c>
       <c r="C250" t="n">
-        <v>155.8999938964844</v>
+        <v>157.4100036621094</v>
       </c>
       <c r="D250" t="n">
-        <v>143455000</v>
+        <v>152962500</v>
       </c>
       <c r="E250" t="n">
         <v>9.012799999999999</v>
       </c>
       <c r="F250" t="n">
-        <v>17.29762048381018</v>
+        <v>17.46516106671727</v>
       </c>
       <c r="G250" t="n">
         <v>751380500</v>
       </c>
       <c r="H250" t="n">
-        <v>117140215363.9374</v>
+        <v>118274807256.6376</v>
       </c>
       <c r="I250" t="n">
-        <v>0.190921909738142</v>
+        <v>0.2035752857573493</v>
       </c>
     </row>
   </sheetData>
@@ -7157,75 +7169,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7261,13 +7273,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40394</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7303,13 +7315,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40491</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7345,13 +7357,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7378,7 +7390,7 @@
       <c r="I5" t="n">
         <v>0.3952</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K5" t="n">
@@ -7391,13 +7403,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7424,7 +7436,7 @@
       <c r="I6" t="n">
         <v>0.4164</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K6" t="n">
@@ -7437,13 +7449,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40394</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7470,7 +7482,7 @@
       <c r="I7" t="n">
         <v>0.4516</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K7" t="n">
@@ -7483,13 +7495,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40491</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7516,7 +7528,7 @@
       <c r="I8" t="n">
         <v>0.3712000000000001</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K8" t="n">
@@ -7529,13 +7541,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7562,7 +7574,7 @@
       <c r="I9" t="n">
         <v>0.4156000000000001</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K9" t="n">
@@ -7575,13 +7587,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7608,7 +7620,7 @@
       <c r="I10" t="n">
         <v>0.4552</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="K10" t="n">
@@ -7621,13 +7633,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7654,7 +7666,7 @@
       <c r="I11" t="n">
         <v>0.5656</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="K11" t="n">
@@ -7667,13 +7679,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40726</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40854</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7700,7 +7712,7 @@
       <c r="I12" t="n">
         <v>0.756</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40854</v>
       </c>
       <c r="K12" t="n">
@@ -7713,13 +7725,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40966</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7746,7 +7758,7 @@
       <c r="I13" t="n">
         <v>0.8260000000000001</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40966</v>
       </c>
       <c r="K13" t="n">
@@ -7759,13 +7771,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>41038</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7792,7 +7804,7 @@
       <c r="I14" t="n">
         <v>0.8855999999999999</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>41038</v>
       </c>
       <c r="K14" t="n">
@@ -7805,13 +7817,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>41128</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7838,7 +7850,7 @@
       <c r="I15" t="n">
         <v>0.9600000000000002</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>41128</v>
       </c>
       <c r="K15" t="n">
@@ -7851,13 +7863,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41214</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7884,7 +7896,7 @@
       <c r="I16" t="n">
         <v>1.0596</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41214</v>
       </c>
       <c r="K16" t="n">
@@ -7897,13 +7909,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41332</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7930,7 +7942,7 @@
       <c r="I17" t="n">
         <v>1.1084</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41332</v>
       </c>
       <c r="K17" t="n">
@@ -7943,13 +7955,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41403</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -7976,7 +7988,7 @@
       <c r="I18" t="n">
         <v>1.1572</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41403</v>
       </c>
       <c r="K18" t="n">
@@ -7989,13 +8001,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41494</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8022,7 +8034,7 @@
       <c r="I19" t="n">
         <v>1.2176</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41494</v>
       </c>
       <c r="K19" t="n">
@@ -8035,13 +8047,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41585</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8068,7 +8080,7 @@
       <c r="I20" t="n">
         <v>1.38</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41585</v>
       </c>
       <c r="K20" t="n">
@@ -8081,13 +8093,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41690</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8114,7 +8126,7 @@
       <c r="I21" t="n">
         <v>1.4404</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41690</v>
       </c>
       <c r="K21" t="n">
@@ -8127,13 +8139,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41767</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8160,7 +8172,7 @@
       <c r="I22" t="n">
         <v>1.5</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41767</v>
       </c>
       <c r="K22" t="n">
@@ -8173,13 +8185,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41862</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8206,7 +8218,7 @@
       <c r="I23" t="n">
         <v>1.6</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41862</v>
       </c>
       <c r="K23" t="n">
@@ -8219,13 +8231,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41947</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8252,7 +8264,7 @@
       <c r="I24" t="n">
         <v>1.7724</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41947</v>
       </c>
       <c r="K24" t="n">
@@ -8265,13 +8277,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>42054</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8298,7 +8310,7 @@
       <c r="I25" t="n">
         <v>1.8292</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>42054</v>
       </c>
       <c r="K25" t="n">
@@ -8311,13 +8323,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42131</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8344,7 +8356,7 @@
       <c r="I26" t="n">
         <v>1.8336</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42131</v>
       </c>
       <c r="K26" t="n">
@@ -8357,13 +8369,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42221</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8390,7 +8402,7 @@
       <c r="I27" t="n">
         <v>1.7956</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42221</v>
       </c>
       <c r="K27" t="n">
@@ -8403,13 +8415,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42317</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8436,7 +8448,7 @@
       <c r="I28" t="n">
         <v>1.9308</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42317</v>
       </c>
       <c r="K28" t="n">
@@ -8449,13 +8461,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42417</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8482,7 +8494,7 @@
       <c r="I29" t="n">
         <v>1.9884</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42417</v>
       </c>
       <c r="K29" t="n">
@@ -8495,13 +8507,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42494</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8528,7 +8540,7 @@
       <c r="I30" t="n">
         <v>2.0328</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42494</v>
       </c>
       <c r="K30" t="n">
@@ -8541,13 +8553,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42586</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8574,7 +8586,7 @@
       <c r="I31" t="n">
         <v>2.0992</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42586</v>
       </c>
       <c r="K31" t="n">
@@ -8587,13 +8599,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42681</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8620,7 +8632,7 @@
       <c r="I32" t="n">
         <v>1.568</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42681</v>
       </c>
       <c r="K32" t="n">
@@ -8633,13 +8645,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42793</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8666,7 +8678,7 @@
       <c r="I33" t="n">
         <v>1.7068</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42793</v>
       </c>
       <c r="K33" t="n">
@@ -8679,13 +8691,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42864</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8712,7 +8724,7 @@
       <c r="I34" t="n">
         <v>1.7724</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42864</v>
       </c>
       <c r="K34" t="n">
@@ -8725,13 +8737,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42955</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8758,7 +8770,7 @@
       <c r="I35" t="n">
         <v>1.884</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42955</v>
       </c>
       <c r="K35" t="n">
@@ -8771,13 +8783,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>43046</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8804,7 +8816,7 @@
       <c r="I36" t="n">
         <v>2.856</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>43046</v>
       </c>
       <c r="K36" t="n">
@@ -8817,13 +8829,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43158</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8850,7 +8862,7 @@
       <c r="I37" t="n">
         <v>1.8608</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43158</v>
       </c>
       <c r="K37" t="n">
@@ -8863,13 +8875,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43229</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8896,7 +8908,7 @@
       <c r="I38" t="n">
         <v>1.99</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43229</v>
       </c>
       <c r="K38" t="n">
@@ -8909,13 +8921,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43321</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8942,7 +8954,7 @@
       <c r="I39" t="n">
         <v>2.2196</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43321</v>
       </c>
       <c r="K39" t="n">
@@ -8955,13 +8967,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43409</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -8988,7 +9000,7 @@
       <c r="I40" t="n">
         <v>2.3232</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43409</v>
       </c>
       <c r="K40" t="n">
@@ -9001,13 +9013,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43523</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9034,7 +9046,7 @@
       <c r="I41" t="n">
         <v>3.334</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43523</v>
       </c>
       <c r="K41" t="n">
@@ -9047,13 +9059,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43594</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9080,7 +9092,7 @@
       <c r="I42" t="n">
         <v>3.5144</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43594</v>
       </c>
       <c r="K42" t="n">
@@ -9093,13 +9105,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43684</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9126,7 +9138,7 @@
       <c r="I43" t="n">
         <v>3.6068</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43684</v>
       </c>
       <c r="K43" t="n">
@@ -9139,13 +9151,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43776</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9172,7 +9184,7 @@
       <c r="I44" t="n">
         <v>3.9476</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43776</v>
       </c>
       <c r="K44" t="n">
@@ -9185,13 +9197,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43887</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9218,7 +9230,7 @@
       <c r="I45" t="n">
         <v>4.503200000000001</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43887</v>
       </c>
       <c r="K45" t="n">
@@ -9231,13 +9243,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43958</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9264,7 +9276,7 @@
       <c r="I46" t="n">
         <v>3.1488</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43958</v>
       </c>
       <c r="K46" t="n">
@@ -9277,13 +9289,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>44049</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9310,7 +9322,7 @@
       <c r="I47" t="n">
         <v>2.37</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>44049</v>
       </c>
       <c r="K47" t="n">
@@ -9323,13 +9335,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44140</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9356,7 +9368,7 @@
       <c r="I48" t="n">
         <v>1.328</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44140</v>
       </c>
       <c r="K48" t="n">
@@ -9369,13 +9381,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44251</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9402,7 +9414,7 @@
       <c r="I49" t="n">
         <v>0.05759999999999998</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44251</v>
       </c>
       <c r="K49" t="n">
@@ -9415,13 +9427,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44321</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9448,7 +9460,7 @@
       <c r="I50" t="n">
         <v>0.6844000000000001</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44321</v>
       </c>
       <c r="K50" t="n">
@@ -9461,13 +9473,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44412</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9494,7 +9506,7 @@
       <c r="I51" t="n">
         <v>0.4024000000000001</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44412</v>
       </c>
       <c r="K51" t="n">
@@ -9507,13 +9519,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44503</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9540,7 +9552,7 @@
       <c r="I52" t="n">
         <v>0.3668000000000002</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44503</v>
       </c>
       <c r="K52" t="n">
@@ -9553,13 +9565,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44615</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9586,7 +9598,7 @@
       <c r="I53" t="n">
         <v>1.1268</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44615</v>
       </c>
       <c r="K53" t="n">
@@ -9599,13 +9611,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44685</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9632,7 +9644,7 @@
       <c r="I54" t="n">
         <v>0.4964000000000001</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44685</v>
       </c>
       <c r="K54" t="n">
@@ -9645,13 +9657,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44776</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9678,7 +9690,7 @@
       <c r="I55" t="n">
         <v>1.5024</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44776</v>
       </c>
       <c r="K55" t="n">
@@ -9691,13 +9703,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44867</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9724,7 +9736,7 @@
       <c r="I56" t="n">
         <v>2.4376</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44867</v>
       </c>
       <c r="K56" t="n">
@@ -9737,13 +9749,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44980</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9770,7 +9782,7 @@
       <c r="I57" t="n">
         <v>3.054</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44980</v>
       </c>
       <c r="K57" t="n">
@@ -9783,13 +9795,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>45050</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9816,7 +9828,7 @@
       <c r="I58" t="n">
         <v>4.018000000000001</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>45050</v>
       </c>
       <c r="K58" t="n">
@@ -9829,13 +9841,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9862,7 +9874,7 @@
       <c r="I59" t="n">
         <v>4.5708</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="K59" t="n">
@@ -9875,13 +9887,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9908,7 +9920,7 @@
       <c r="I60" t="n">
         <v>5.6836</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="K60" t="n">
@@ -9921,13 +9933,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45344</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9954,7 +9966,7 @@
       <c r="I61" t="n">
         <v>4.696000000000001</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45344</v>
       </c>
       <c r="K61" t="n">
@@ -9967,13 +9979,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10000,7 +10012,7 @@
       <c r="I62" t="n">
         <v>5.3108</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="K62" t="n">
@@ -10013,13 +10025,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10046,7 +10058,7 @@
       <c r="I63" t="n">
         <v>5.6904</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="K63" t="n">
@@ -10059,13 +10071,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45595</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10092,7 +10104,7 @@
       <c r="I64" t="n">
         <v>5.872000000000001</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45595</v>
       </c>
       <c r="K64" t="n">
@@ -10105,13 +10117,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45708</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10138,7 +10150,7 @@
       <c r="I65" t="n">
         <v>6.9076</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45708</v>
       </c>
       <c r="K65" t="n">
@@ -10151,13 +10163,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45776</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10184,7 +10196,7 @@
       <c r="I66" t="n">
         <v>6.4156</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45776</v>
       </c>
       <c r="K66" t="n">
@@ -10197,13 +10209,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45867</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10230,7 +10242,7 @@
       <c r="I67" t="n">
         <v>5.7376</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45867</v>
       </c>
       <c r="K67" t="n">
@@ -10243,13 +10255,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45958</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10276,7 +10288,7 @@
       <c r="I68" t="n">
         <v>6.1404</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45958</v>
       </c>
       <c r="K68" t="n">
@@ -10289,13 +10301,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>46071</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10322,7 +10334,7 @@
       <c r="I69" t="n">
         <v>6.6228</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>46071</v>
       </c>
       <c r="K69" t="n">
@@ -10335,13 +10347,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>46140</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10368,7 +10380,7 @@
       <c r="I70" t="n">
         <v>7.579999999999999</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>46140</v>
       </c>
       <c r="K70" t="n">
@@ -10381,13 +10393,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46238</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10414,7 +10426,7 @@
       <c r="I71" t="n">
         <v>9.012799999999999</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46238</v>
       </c>
       <c r="K71" t="n">
@@ -10451,52 +10463,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40387</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40394</v>
       </c>
       <c r="C2" t="n">
@@ -10525,10 +10537,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40484</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40491</v>
       </c>
       <c r="C3" t="n">
@@ -10557,10 +10569,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40591</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="C4" t="n">
@@ -10589,10 +10601,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40662</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="C5" t="n">
@@ -10621,10 +10633,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40753</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="C6" t="n">
@@ -10653,10 +10665,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40847</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40854</v>
       </c>
       <c r="C7" t="n">
@@ -10685,10 +10697,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40956</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40966</v>
       </c>
       <c r="C8" t="n">
@@ -10717,10 +10729,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>41031</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>41038</v>
       </c>
       <c r="C9" t="n">
@@ -10749,10 +10761,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>41121</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>41128</v>
       </c>
       <c r="C10" t="n">
@@ -10781,10 +10793,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>41208</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>41214</v>
       </c>
       <c r="C11" t="n">
@@ -10813,10 +10825,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41325</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41332</v>
       </c>
       <c r="C12" t="n">
@@ -10845,10 +10857,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41396</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41403</v>
       </c>
       <c r="C13" t="n">
@@ -10877,10 +10889,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41487</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41494</v>
       </c>
       <c r="C14" t="n">
@@ -10909,10 +10921,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41579</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41585</v>
       </c>
       <c r="C15" t="n">
@@ -10941,10 +10953,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41683</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41690</v>
       </c>
       <c r="C16" t="n">
@@ -10973,10 +10985,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41760</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41767</v>
       </c>
       <c r="C17" t="n">
@@ -11005,10 +11017,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41852</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41862</v>
       </c>
       <c r="C18" t="n">
@@ -11037,10 +11049,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41939</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41947</v>
       </c>
       <c r="C19" t="n">
@@ -11069,10 +11081,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>42046</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>42054</v>
       </c>
       <c r="C20" t="n">
@@ -11101,10 +11113,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>42124</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>42131</v>
       </c>
       <c r="C21" t="n">
@@ -11133,10 +11145,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>42214</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>42221</v>
       </c>
       <c r="C22" t="n">
@@ -11165,10 +11177,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42310</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42317</v>
       </c>
       <c r="C23" t="n">
@@ -11197,10 +11209,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42409</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42417</v>
       </c>
       <c r="C24" t="n">
@@ -11229,10 +11241,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42486</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42494</v>
       </c>
       <c r="C25" t="n">
@@ -11261,10 +11273,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42579</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42586</v>
       </c>
       <c r="C26" t="n">
@@ -11293,10 +11305,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42674</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42681</v>
       </c>
       <c r="C27" t="n">
@@ -11325,10 +11337,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42787</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42793</v>
       </c>
       <c r="C28" t="n">
@@ -11357,10 +11369,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42857</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42864</v>
       </c>
       <c r="C29" t="n">
@@ -11389,10 +11401,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42948</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42955</v>
       </c>
       <c r="C30" t="n">
@@ -11421,10 +11433,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>43038</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>43046</v>
       </c>
       <c r="C31" t="n">
@@ -11453,10 +11465,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>43151</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>43158</v>
       </c>
       <c r="C32" t="n">
@@ -11485,10 +11497,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>43222</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>43229</v>
       </c>
       <c r="C33" t="n">
@@ -11517,10 +11529,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43313</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43321</v>
       </c>
       <c r="C34" t="n">
@@ -11549,10 +11561,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43402</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43409</v>
       </c>
       <c r="C35" t="n">
@@ -11581,10 +11593,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43516</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43523</v>
       </c>
       <c r="C36" t="n">
@@ -11613,10 +11625,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43587</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43594</v>
       </c>
       <c r="C37" t="n">
@@ -11645,10 +11657,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43677</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43684</v>
       </c>
       <c r="C38" t="n">
@@ -11677,10 +11689,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43769</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43776</v>
       </c>
       <c r="C39" t="n">
@@ -11709,10 +11721,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43880</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43887</v>
       </c>
       <c r="C40" t="n">
@@ -11741,10 +11753,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43951</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43958</v>
       </c>
       <c r="C41" t="n">
@@ -11773,10 +11785,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>44042</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>44049</v>
       </c>
       <c r="C42" t="n">
@@ -11805,10 +11817,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>44133</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>44140</v>
       </c>
       <c r="C43" t="n">
@@ -11837,10 +11849,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>44244</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>44251</v>
       </c>
       <c r="C44" t="n">
@@ -11869,10 +11881,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44314</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44321</v>
       </c>
       <c r="C45" t="n">
@@ -11901,10 +11913,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44405</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44412</v>
       </c>
       <c r="C46" t="n">
@@ -11933,10 +11945,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44496</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44503</v>
       </c>
       <c r="C47" t="n">
@@ -11965,10 +11977,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44608</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44615</v>
       </c>
       <c r="C48" t="n">
@@ -11997,10 +12009,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44678</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44685</v>
       </c>
       <c r="C49" t="n">
@@ -12029,10 +12041,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44769</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44776</v>
       </c>
       <c r="C50" t="n">
@@ -12061,10 +12073,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44860</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44867</v>
       </c>
       <c r="C51" t="n">
@@ -12093,10 +12105,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44973</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44980</v>
       </c>
       <c r="C52" t="n">
@@ -12125,10 +12137,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>45043</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>45050</v>
       </c>
       <c r="C53" t="n">
@@ -12157,10 +12169,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>45134</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="C54" t="n">
@@ -12189,10 +12201,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45225</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="C55" t="n">
@@ -12221,10 +12233,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45337</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45344</v>
       </c>
       <c r="C56" t="n">
@@ -12253,10 +12265,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45407</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="C57" t="n">
@@ -12285,10 +12297,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45498</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="C58" t="n">
@@ -12317,10 +12329,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45588</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45595</v>
       </c>
       <c r="C59" t="n">
@@ -12349,10 +12361,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45701</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45708</v>
       </c>
       <c r="C60" t="n">
@@ -12381,10 +12393,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45768</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45776</v>
       </c>
       <c r="C61" t="n">
@@ -12413,10 +12425,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45859</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45867</v>
       </c>
       <c r="C62" t="n">
@@ -12445,10 +12457,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45950</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45958</v>
       </c>
       <c r="C63" t="n">
@@ -12477,10 +12489,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>46063</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>46071</v>
       </c>
       <c r="C64" t="n">
@@ -12509,10 +12521,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>46132</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>46140</v>
       </c>
       <c r="C65" t="n">
@@ -12541,10 +12553,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>46230</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>46238</v>
       </c>
       <c r="C66" t="n">
@@ -12591,12 +12603,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/BKNG.xlsx
+++ b/salidas/empresas/BKNG.xlsx
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>0.9592574834823608</v>
+        <v>0.9592576026916504</v>
       </c>
       <c r="C3" t="n">
         <v>0.9819999933242798</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>0.970588743686676</v>
+        <v>0.9705888628959656</v>
       </c>
       <c r="C4" t="n">
         <v>0.9936000108718872</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>1.215189695358276</v>
+        <v>1.215189456939697</v>
       </c>
       <c r="C6" t="n">
         <v>1.24399995803833</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>1.30505895614624</v>
+        <v>1.305059194564819</v>
       </c>
       <c r="C9" t="n">
         <v>1.335999965667725</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>1.437518835067749</v>
+        <v>1.43751859664917</v>
       </c>
       <c r="C10" t="n">
         <v>1.47160005569458</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>1.574276447296143</v>
+        <v>1.574276566505432</v>
       </c>
       <c r="C11" t="n">
         <v>1.611600041389465</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>1.70400071144104</v>
+        <v>1.70400083065033</v>
       </c>
       <c r="C13" t="n">
         <v>1.744400024414062</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>1.665317893028259</v>
+        <v>1.665318012237549</v>
       </c>
       <c r="C14" t="n">
         <v>1.704800009727478</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>2.04784893989563</v>
+        <v>2.047848463058472</v>
       </c>
       <c r="C15" t="n">
         <v>2.096400022506714</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>2.081061124801636</v>
+        <v>2.081061363220215</v>
       </c>
       <c r="C16" t="n">
         <v>2.130399942398071</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>2.174056053161621</v>
+        <v>2.174056529998779</v>
       </c>
       <c r="C17" t="n">
         <v>2.225600004196167</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>2.416312456130981</v>
+        <v>2.416312694549561</v>
       </c>
       <c r="C18" t="n">
         <v>2.473599910736084</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>2.685920476913452</v>
+        <v>2.68592095375061</v>
       </c>
       <c r="C19" t="n">
         <v>2.749599933624268</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>3.46778416633606</v>
+        <v>3.46778392791748</v>
       </c>
       <c r="C22" t="n">
         <v>3.549999952316284</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>4.446578502655029</v>
+        <v>4.446578025817871</v>
       </c>
       <c r="C24" t="n">
         <v>4.552000045776367</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>4.487997055053711</v>
+        <v>4.487996578216553</v>
       </c>
       <c r="C25" t="n">
         <v>4.594399929046631</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>4.455174922943115</v>
+        <v>4.455175399780273</v>
       </c>
       <c r="C27" t="n">
         <v>4.560800075531006</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>4.722438812255859</v>
+        <v>4.722437858581543</v>
       </c>
       <c r="C28" t="n">
         <v>4.834400177001953</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>5.256574630737305</v>
+        <v>5.256575107574463</v>
       </c>
       <c r="C30" t="n">
         <v>5.381199836730957</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>4.511441230773926</v>
+        <v>4.511440753936768</v>
       </c>
       <c r="C31" t="n">
         <v>4.618400096893311</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>3.633065938949585</v>
+        <v>3.633065462112427</v>
       </c>
       <c r="C33" t="n">
         <v>3.719199895858765</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>2.673808097839355</v>
+        <v>2.673807859420776</v>
       </c>
       <c r="C34" t="n">
         <v>2.737200021743774</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>2.056445121765137</v>
+        <v>2.056444406509399</v>
       </c>
       <c r="C35" t="n">
         <v>2.105200052261353</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>2.696080207824707</v>
+        <v>2.696080446243286</v>
       </c>
       <c r="C36" t="n">
         <v>2.759999990463257</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>2.877772808074951</v>
+        <v>2.87777304649353</v>
       </c>
       <c r="C37" t="n">
         <v>2.946000099182129</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>2.62144947052002</v>
+        <v>2.621449947357178</v>
       </c>
       <c r="C38" t="n">
         <v>2.683599948883057</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>3.31578803062439</v>
+        <v>3.315787792205811</v>
       </c>
       <c r="C39" t="n">
         <v>3.394399881362915</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>3.078220129013062</v>
+        <v>3.078220367431641</v>
       </c>
       <c r="C40" t="n">
         <v>3.15120005607605</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>5.064723491668701</v>
+        <v>5.064722537994385</v>
       </c>
       <c r="C44" t="n">
         <v>5.184800148010254</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>6.016557693481445</v>
+        <v>6.016556262969971</v>
       </c>
       <c r="C45" t="n">
         <v>6.159200191497803</v>
@@ -1334,7 +1334,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>6.479188919067383</v>
+        <v>6.479187965393066</v>
       </c>
       <c r="C46" t="n">
         <v>6.632800102233887</v>
@@ -1391,7 +1391,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>8.534069061279297</v>
+        <v>8.53407096862793</v>
       </c>
       <c r="C49" t="n">
         <v>8.73639965057373</v>
@@ -1410,7 +1410,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>7.633033275604248</v>
+        <v>7.63303279876709</v>
       </c>
       <c r="C50" t="n">
         <v>7.814000129699707</v>
@@ -1429,7 +1429,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>8.858382225036621</v>
+        <v>8.858383178710938</v>
       </c>
       <c r="C51" t="n">
         <v>9.068400382995605</v>
@@ -1486,7 +1486,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>7.469313621520996</v>
+        <v>7.469314575195312</v>
       </c>
       <c r="C54" t="n">
         <v>7.646399974822998</v>
@@ -1505,7 +1505,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>6.898058891296387</v>
+        <v>6.898057460784912</v>
       </c>
       <c r="C55" t="n">
         <v>7.061600208282471</v>
@@ -1524,7 +1524,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>8.768122673034668</v>
+        <v>8.768120765686035</v>
       </c>
       <c r="C56" t="n">
         <v>8.97599983215332</v>
@@ -1543,7 +1543,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>11.38917922973633</v>
+        <v>11.38918018341064</v>
       </c>
       <c r="C57" t="n">
         <v>11.65919971466064</v>
@@ -1568,7 +1568,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>13.61090564727783</v>
+        <v>13.61090850830078</v>
       </c>
       <c r="C58" t="n">
         <v>13.93360042572021</v>
@@ -1593,7 +1593,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>14.72333335876465</v>
+        <v>14.72332954406738</v>
       </c>
       <c r="C59" t="n">
         <v>15.07240009307861</v>
@@ -1618,7 +1618,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>15.39696216583252</v>
+        <v>15.3969612121582</v>
       </c>
       <c r="C60" t="n">
         <v>15.76200008392334</v>
@@ -1643,7 +1643,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>15.61186695098877</v>
+        <v>15.61186599731445</v>
       </c>
       <c r="C61" t="n">
         <v>15.98200035095215</v>
@@ -1693,7 +1693,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>17.7347354888916</v>
+        <v>17.73473358154297</v>
       </c>
       <c r="C63" t="n">
         <v>18.15519905090332</v>
@@ -1722,7 +1722,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>19.7884464263916</v>
+        <v>19.78844451904297</v>
       </c>
       <c r="C64" t="n">
         <v>20.25760078430176</v>
@@ -1838,7 +1838,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>21.00793266296387</v>
+        <v>21.00793647766113</v>
       </c>
       <c r="C68" t="n">
         <v>21.50600051879883</v>
@@ -1896,7 +1896,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>17.56203079223633</v>
+        <v>17.5620288848877</v>
       </c>
       <c r="C70" t="n">
         <v>17.9783992767334</v>
@@ -1925,7 +1925,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>19.83845901489258</v>
+        <v>19.83846282958984</v>
       </c>
       <c r="C71" t="n">
         <v>20.30879974365234</v>
@@ -1954,7 +1954,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>18.9854850769043</v>
+        <v>18.98548316955566</v>
       </c>
       <c r="C72" t="n">
         <v>19.43560028076172</v>
@@ -1983,7 +1983,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>18.27512550354004</v>
+        <v>18.27512741088867</v>
       </c>
       <c r="C73" t="n">
         <v>18.70840072631836</v>
@@ -2012,7 +2012,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>20.68909454345703</v>
+        <v>20.68909072875977</v>
       </c>
       <c r="C74" t="n">
         <v>21.17959976196289</v>
@@ -2041,7 +2041,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>24.49994087219238</v>
+        <v>24.49994468688965</v>
       </c>
       <c r="C75" t="n">
         <v>25.0807991027832</v>
@@ -2070,7 +2070,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>28.03532791137695</v>
+        <v>28.03532409667969</v>
       </c>
       <c r="C76" t="n">
         <v>28.70000076293945</v>
@@ -2099,7 +2099,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>29.72799491882324</v>
+        <v>29.72799301147461</v>
       </c>
       <c r="C77" t="n">
         <v>30.43280029296875</v>
@@ -2128,7 +2128,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>24.44016075134277</v>
+        <v>24.44016456604004</v>
       </c>
       <c r="C78" t="n">
         <v>25.01959991455078</v>
@@ -2186,7 +2186,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>25.85658073425293</v>
+        <v>25.85658264160156</v>
       </c>
       <c r="C80" t="n">
         <v>26.46960067749023</v>
@@ -2215,7 +2215,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>23.62273979187012</v>
+        <v>23.62274169921875</v>
       </c>
       <c r="C81" t="n">
         <v>24.18280029296875</v>
@@ -2273,7 +2273,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>22.41927528381348</v>
+        <v>22.41927337646484</v>
       </c>
       <c r="C83" t="n">
         <v>22.9507999420166</v>
@@ -2331,7 +2331,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>24.24088668823242</v>
+        <v>24.24088478088379</v>
       </c>
       <c r="C85" t="n">
         <v>24.81559944152832</v>
@@ -2360,7 +2360,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>26.78380012512207</v>
+        <v>26.7838020324707</v>
       </c>
       <c r="C86" t="n">
         <v>27.41880035400391</v>
@@ -2389,7 +2389,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>26.926025390625</v>
+        <v>26.92602729797363</v>
       </c>
       <c r="C87" t="n">
         <v>27.56439971923828</v>
@@ -2418,7 +2418,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>26.88890838623047</v>
+        <v>26.88890647888184</v>
       </c>
       <c r="C88" t="n">
         <v>27.52639961242676</v>
@@ -2476,7 +2476,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>31.41246032714844</v>
+        <v>31.41245651245117</v>
       </c>
       <c r="C90" t="n">
         <v>32.15719985961914</v>
@@ -2534,7 +2534,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>34.21560287475586</v>
+        <v>34.21559906005859</v>
       </c>
       <c r="C92" t="n">
         <v>35.02679824829102</v>
@@ -2563,7 +2563,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>36.67177200317383</v>
+        <v>36.67176818847656</v>
       </c>
       <c r="C93" t="n">
         <v>37.54119873046875</v>
@@ -2592,7 +2592,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>39.50148391723633</v>
+        <v>39.5014762878418</v>
       </c>
       <c r="C94" t="n">
         <v>40.4379997253418</v>
@@ -2708,7 +2708,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>44.73500442504883</v>
+        <v>44.73500061035156</v>
       </c>
       <c r="C98" t="n">
         <v>45.79560089111328</v>
@@ -2737,7 +2737,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>52.70406723022461</v>
+        <v>52.70407104492188</v>
       </c>
       <c r="C99" t="n">
         <v>53.9536018371582</v>
@@ -2766,7 +2766,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>46.57145690917969</v>
+        <v>46.57145309448242</v>
       </c>
       <c r="C100" t="n">
         <v>47.67559814453125</v>
@@ -2795,7 +2795,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>45.23748779296875</v>
+        <v>45.23749160766602</v>
       </c>
       <c r="C101" t="n">
         <v>46.31000137329102</v>
@@ -2882,7 +2882,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>48.54701995849609</v>
+        <v>48.54702758789062</v>
       </c>
       <c r="C104" t="n">
         <v>49.69800186157227</v>
@@ -2911,7 +2911,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>48.61970138549805</v>
+        <v>48.61970901489258</v>
       </c>
       <c r="C105" t="n">
         <v>49.77239990234375</v>
@@ -2940,7 +2940,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>45.26991271972656</v>
+        <v>45.26992034912109</v>
       </c>
       <c r="C106" t="n">
         <v>46.34320068359375</v>
@@ -2969,7 +2969,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>47.1309928894043</v>
+        <v>47.13099670410156</v>
       </c>
       <c r="C107" t="n">
         <v>48.2484016418457</v>
@@ -2998,7 +2998,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>45.33283233642578</v>
+        <v>45.33282470703125</v>
       </c>
       <c r="C108" t="n">
         <v>46.40760040283203</v>
@@ -3056,7 +3056,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>39.44404602050781</v>
+        <v>39.44403839111328</v>
       </c>
       <c r="C110" t="n">
         <v>40.37919998168945</v>
@@ -3143,7 +3143,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>48.36572265625</v>
+        <v>48.36572647094727</v>
       </c>
       <c r="C113" t="n">
         <v>49.51240158081055</v>
@@ -3172,7 +3172,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>45.79585266113281</v>
+        <v>45.79584503173828</v>
       </c>
       <c r="C114" t="n">
         <v>46.88159942626953</v>
@@ -3230,7 +3230,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>48.59078216552734</v>
+        <v>48.59078598022461</v>
       </c>
       <c r="C116" t="n">
         <v>49.74280166625977</v>
@@ -3259,7 +3259,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>48.78888702392578</v>
+        <v>48.78889083862305</v>
       </c>
       <c r="C117" t="n">
         <v>49.94559860229492</v>
@@ -3288,7 +3288,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>48.32859802246094</v>
+        <v>48.32860565185547</v>
       </c>
       <c r="C118" t="n">
         <v>49.47439956665039</v>
@@ -3317,7 +3317,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>56.82242965698242</v>
+        <v>56.82242584228516</v>
       </c>
       <c r="C119" t="n">
         <v>58.16960144042969</v>
@@ -3346,7 +3346,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>48.79709625244141</v>
+        <v>48.79709243774414</v>
       </c>
       <c r="C120" t="n">
         <v>49.95399856567383</v>
@@ -3375,7 +3375,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>49.81691741943359</v>
+        <v>49.81691360473633</v>
       </c>
       <c r="C121" t="n">
         <v>50.99800109863281</v>
@@ -3404,7 +3404,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>41.61223983764648</v>
+        <v>41.61223602294922</v>
       </c>
       <c r="C122" t="n">
         <v>42.59880065917969</v>
@@ -3520,7 +3520,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>49.40195083618164</v>
+        <v>49.40195846557617</v>
       </c>
       <c r="C126" t="n">
         <v>50.57320022583008</v>
@@ -3549,7 +3549,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>48.77989959716797</v>
+        <v>48.7799072265625</v>
       </c>
       <c r="C127" t="n">
         <v>49.9364013671875</v>
@@ -3607,7 +3607,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>55.35678482055664</v>
+        <v>55.35677719116211</v>
       </c>
       <c r="C129" t="n">
         <v>56.6692008972168</v>
@@ -3665,7 +3665,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>57.6035041809082</v>
+        <v>57.60350799560547</v>
       </c>
       <c r="C131" t="n">
         <v>58.96920013427734</v>
@@ -3723,7 +3723,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>57.28427505493164</v>
+        <v>57.28428268432617</v>
       </c>
       <c r="C133" t="n">
         <v>58.64239883422852</v>
@@ -3839,7 +3839,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>72.16194915771484</v>
+        <v>72.16195678710938</v>
       </c>
       <c r="C137" t="n">
         <v>73.872802734375</v>
@@ -3955,7 +3955,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>72.36748504638672</v>
+        <v>72.36747741699219</v>
       </c>
       <c r="C141" t="n">
         <v>74.08319854736328</v>
@@ -3984,7 +3984,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>71.53677368164062</v>
+        <v>71.53678131103516</v>
       </c>
       <c r="C142" t="n">
         <v>73.23280334472656</v>
@@ -4013,7 +4013,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>74.70721435546875</v>
+        <v>74.70722198486328</v>
       </c>
       <c r="C143" t="n">
         <v>76.47840118408203</v>
@@ -4100,7 +4100,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>74.71073913574219</v>
+        <v>74.71073150634766</v>
       </c>
       <c r="C146" t="n">
         <v>76.48200225830078</v>
@@ -4129,7 +4129,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>79.47731018066406</v>
+        <v>79.47731781005859</v>
       </c>
       <c r="C147" t="n">
         <v>81.36160278320312</v>
@@ -4216,7 +4216,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>82.40316009521484</v>
+        <v>82.40315246582031</v>
       </c>
       <c r="C150" t="n">
         <v>84.35679626464844</v>
@@ -4303,7 +4303,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>76.25413513183594</v>
+        <v>76.25412750244141</v>
       </c>
       <c r="C153" t="n">
         <v>78.06199645996094</v>
@@ -4332,7 +4332,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>77.52207183837891</v>
+        <v>77.52206420898438</v>
       </c>
       <c r="C154" t="n">
         <v>79.36000061035156</v>
@@ -4419,7 +4419,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>67.30118560791016</v>
+        <v>67.30117797851562</v>
       </c>
       <c r="C157" t="n">
         <v>68.89679718017578</v>
@@ -4477,7 +4477,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>66.30949401855469</v>
+        <v>66.30950164794922</v>
       </c>
       <c r="C159" t="n">
         <v>67.88159942626953</v>
@@ -4506,7 +4506,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>68.17996978759766</v>
+        <v>68.17996215820312</v>
       </c>
       <c r="C160" t="n">
         <v>69.79640197753906</v>
@@ -4564,7 +4564,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>64.71453094482422</v>
+        <v>64.71451568603516</v>
       </c>
       <c r="C162" t="n">
         <v>66.24880218505859</v>
@@ -4593,7 +4593,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>73.251708984375</v>
+        <v>73.25171661376953</v>
       </c>
       <c r="C163" t="n">
         <v>74.9884033203125</v>
@@ -4622,7 +4622,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>73.71669769287109</v>
+        <v>73.71669006347656</v>
       </c>
       <c r="C164" t="n">
         <v>75.46440124511719</v>
@@ -4680,7 +4680,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>76.68628692626953</v>
+        <v>76.686279296875</v>
       </c>
       <c r="C166" t="n">
         <v>78.50440216064453</v>
@@ -4709,7 +4709,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>80.05287170410156</v>
+        <v>80.05287933349609</v>
       </c>
       <c r="C167" t="n">
         <v>81.95079803466797</v>
@@ -4854,7 +4854,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>52.56653213500977</v>
+        <v>52.5665283203125</v>
       </c>
       <c r="C172" t="n">
         <v>53.81280136108398</v>
@@ -4883,7 +4883,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>57.85124206542969</v>
+        <v>57.85123825073242</v>
       </c>
       <c r="C173" t="n">
         <v>59.22280120849609</v>
@@ -4912,7 +4912,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>64.05808258056641</v>
+        <v>64.05809020996094</v>
       </c>
       <c r="C174" t="n">
         <v>65.57679748535156</v>
@@ -4941,7 +4941,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>62.21849060058594</v>
+        <v>62.2184944152832</v>
       </c>
       <c r="C175" t="n">
         <v>63.69359970092773</v>
@@ -4970,7 +4970,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>64.94544219970703</v>
+        <v>64.9454345703125</v>
       </c>
       <c r="C176" t="n">
         <v>66.48519897460938</v>
@@ -5057,7 +5057,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>63.39694976806641</v>
+        <v>63.3969612121582</v>
       </c>
       <c r="C179" t="n">
         <v>64.90000152587891</v>
@@ -5115,7 +5115,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>87.02751159667969</v>
+        <v>87.02750396728516</v>
       </c>
       <c r="C181" t="n">
         <v>89.09079742431641</v>
@@ -5144,7 +5144,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>75.97203063964844</v>
+        <v>75.97202301025391</v>
       </c>
       <c r="C182" t="n">
         <v>77.77320098876953</v>
@@ -5202,7 +5202,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>91.03529357910156</v>
+        <v>91.03530120849609</v>
       </c>
       <c r="C184" t="n">
         <v>93.193603515625</v>
@@ -5231,7 +5231,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>96.35869598388672</v>
+        <v>96.35868835449219</v>
       </c>
       <c r="C185" t="n">
         <v>98.64320373535156</v>
@@ -5260,7 +5260,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>92.27430725097656</v>
+        <v>92.27431488037109</v>
       </c>
       <c r="C186" t="n">
         <v>94.46199798583984</v>
@@ -5347,7 +5347,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>89.85646057128906</v>
+        <v>89.8564453125</v>
       </c>
       <c r="C189" t="n">
         <v>91.98680114746094</v>
@@ -5434,7 +5434,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>82.12689971923828</v>
+        <v>82.12691497802734</v>
       </c>
       <c r="C192" t="n">
         <v>84.07399749755859</v>
@@ -5521,7 +5521,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>84.87769317626953</v>
+        <v>84.87767791748047</v>
       </c>
       <c r="C195" t="n">
         <v>86.88999938964844</v>
@@ -5550,7 +5550,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>91.762451171875</v>
+        <v>91.76247406005859</v>
       </c>
       <c r="C196" t="n">
         <v>93.93800354003906</v>
@@ -5608,7 +5608,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>87.66402435302734</v>
+        <v>87.66403198242188</v>
       </c>
       <c r="C198" t="n">
         <v>89.74240112304688</v>
@@ -5637,7 +5637,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>68.33937835693359</v>
+        <v>68.33938598632812</v>
       </c>
       <c r="C199" t="n">
         <v>69.95960235595703</v>
@@ -5666,7 +5666,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>75.63442230224609</v>
+        <v>75.63441467285156</v>
       </c>
       <c r="C200" t="n">
         <v>77.42759704589844</v>
@@ -5695,7 +5695,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>73.29468536376953</v>
+        <v>73.29470825195312</v>
       </c>
       <c r="C201" t="n">
         <v>75.03240203857422</v>
@@ -5724,7 +5724,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>64.20616149902344</v>
+        <v>64.2061767578125</v>
       </c>
       <c r="C202" t="n">
         <v>65.72840118408203</v>
@@ -5753,7 +5753,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>73.04735565185547</v>
+        <v>73.04736328125</v>
       </c>
       <c r="C203" t="n">
         <v>74.77919769287109</v>
@@ -5840,7 +5840,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>95.10910034179688</v>
+        <v>95.10910797119141</v>
       </c>
       <c r="C206" t="n">
         <v>97.36399841308594</v>
@@ -5869,7 +5869,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>98.62181854248047</v>
+        <v>98.62183380126953</v>
       </c>
       <c r="C207" t="n">
         <v>100.9599990844727</v>
@@ -5898,7 +5898,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>103.6392669677734</v>
+        <v>103.639274597168</v>
       </c>
       <c r="C208" t="n">
         <v>106.0963973999023</v>
@@ -5956,7 +5956,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>98.0267333984375</v>
+        <v>98.02674865722656</v>
       </c>
       <c r="C210" t="n">
         <v>100.3507995605469</v>
@@ -5985,7 +5985,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>105.5116806030273</v>
+        <v>105.5116958618164</v>
       </c>
       <c r="C211" t="n">
         <v>108.0131988525391</v>
@@ -6014,7 +6014,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>116.0799331665039</v>
+        <v>116.0799179077148</v>
       </c>
       <c r="C212" t="n">
         <v>118.8320007324219</v>
@@ -6072,7 +6072,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>120.501106262207</v>
+        <v>120.5011138916016</v>
       </c>
       <c r="C214" t="n">
         <v>123.3580017089844</v>
@@ -6101,7 +6101,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>108.9982223510742</v>
+        <v>108.9982147216797</v>
       </c>
       <c r="C215" t="n">
         <v>111.5823974609375</v>
@@ -6130,7 +6130,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>122.132438659668</v>
+        <v>122.1324310302734</v>
       </c>
       <c r="C216" t="n">
         <v>125.0279998779297</v>
@@ -6188,7 +6188,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>137.0495452880859</v>
+        <v>137.0495910644531</v>
       </c>
       <c r="C218" t="n">
         <v>140.2987976074219</v>
@@ -6217,7 +6217,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>135.5397644042969</v>
+        <v>135.5397796630859</v>
       </c>
       <c r="C219" t="n">
         <v>138.7532043457031</v>
@@ -6246,7 +6246,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>142.1171875</v>
+        <v>142.1171722412109</v>
       </c>
       <c r="C220" t="n">
         <v>145.1152038574219</v>
@@ -6275,7 +6275,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>135.2284851074219</v>
+        <v>135.2285003662109</v>
       </c>
       <c r="C221" t="n">
         <v>138.0812072753906</v>
@@ -6333,7 +6333,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>155.5435180664062</v>
+        <v>155.5435028076172</v>
       </c>
       <c r="C223" t="n">
         <v>158.4600067138672</v>
@@ -6420,7 +6420,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>165.7673187255859</v>
+        <v>165.767333984375</v>
       </c>
       <c r="C226" t="n">
         <v>168.4848022460938</v>
@@ -6449,7 +6449,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>184.0330963134766</v>
+        <v>184.0330810546875</v>
       </c>
       <c r="C227" t="n">
         <v>187.0500030517578</v>
@@ -6507,7 +6507,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>195.8554534912109</v>
+        <v>195.85546875</v>
       </c>
       <c r="C229" t="n">
         <v>198.7368011474609</v>
